--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123388484</v>
       </c>
       <c r="B2" t="n">
-        <v>94886</v>
+        <v>94889</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>123388080</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123388484</v>
       </c>
       <c r="B2" t="n">
-        <v>94889</v>
+        <v>94891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>123388080</v>
       </c>
       <c r="B3" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>94891</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R2" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>100636</v>
+        <v>94897</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R3" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B2" t="n">
-        <v>100642</v>
+        <v>94900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R2" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B3" t="n">
-        <v>94897</v>
+        <v>100645</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +828,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R3" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +913,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>94900</v>
+        <v>100662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R2" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>100645</v>
+        <v>94917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R3" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>William Rosén, Amanda Olsson</t>
+          <t>Amanda Olsson, William Rosén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>94917</v>
+        <v>94923</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Olsson, William Rosén</t>
+          <t>William Rosén, Amanda Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,7 +795,7 @@
         <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>94923</v>
+        <v>94925</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>94925</v>
+        <v>95433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>95433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R2" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B3" t="n">
-        <v>95433</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,27 +828,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R3" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +913,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B2" t="n">
-        <v>95433</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R2" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,26 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>95433</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,27 +808,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R3" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,6 +893,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123388080</v>
+        <v>123388484</v>
       </c>
       <c r="B2" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537451</v>
+        <v>537485</v>
       </c>
       <c r="R2" t="n">
-        <v>6443593</v>
+        <v>6443612</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +771,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,15 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123388484</v>
+        <v>123388080</v>
       </c>
       <c r="B3" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,27 +818,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537485</v>
+        <v>537451</v>
       </c>
       <c r="R3" t="n">
-        <v>6443612</v>
+        <v>6443593</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,26 +903,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 5588-2025 artfynd.xlsx
+++ b/artfynd/A 5588-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -804,6 +809,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123388484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,8 +926,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123388080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>